--- a/UpdateData.xlsx
+++ b/UpdateData.xlsx
@@ -8,12 +8,17 @@
   <sheets>
     <sheet name="UpdateData" r:id="rId3" sheetId="1"/>
     <sheet name="New Sheet" r:id="rId4" sheetId="2"/>
+    <sheet name="New Sheet2" r:id="rId5" sheetId="3"/>
+    <sheet name="New Sheet3" r:id="rId6" sheetId="4"/>
+    <sheet name="New Sheet30.05912091092790106" r:id="rId7" sheetId="5"/>
+    <sheet name="New Sheet30.18429760448441923" r:id="rId8" sheetId="6"/>
+    <sheet name="New Sheet 70.4355004127872629" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="17">
   <si>
     <t>Name</t>
   </si>
@@ -108,7 +113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -177,6 +182,61 @@
         <v>14</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -195,4 +255,79 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>